--- a/Capítulo02/Capítulo02/CONTAS DO FABIO.xlsx
+++ b/Capítulo02/Capítulo02/CONTAS DO FABIO.xlsx
@@ -1,27 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Silvia\Documents\Cursos Office 2016\EXCEL AVANÇADO\PLANILHAS\DO CURSO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://senacspedu-my.sharepoint.com/personal/yuri_smendes_senacsp_edu_br/Documents/Capítulo02/Capítulo02/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="62" documentId="11_5115F023DE706007C05CEF289BC74C123581E232" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{83D6BA55-D828-446E-BE40-3E6366CCAF99}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="105" windowWidth="13395" windowHeight="5190"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
     <sheet name="Plan2" sheetId="2" r:id="rId2"/>
     <sheet name="Plan3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="18">
   <si>
     <t>Nº Parcelas</t>
   </si>
@@ -58,11 +72,29 @@
   <si>
     <t xml:space="preserve">Valor desejado </t>
   </si>
+  <si>
+    <t>FUNÇÕES</t>
+  </si>
+  <si>
+    <t>#=-VF(B5;A5;C5;0) / definindo o valor futuro do investimento</t>
+  </si>
+  <si>
+    <t>#=VP(B9;A9;-C9) / verificando à vista (total) de uma compra</t>
+  </si>
+  <si>
+    <t>#=PGTO(B13;A13;D13) / definindo o valor da parcela de uma compra</t>
+  </si>
+  <si>
+    <t>#=-NPER(B17;C17;D17) / definindo o número de parcelas</t>
+  </si>
+  <si>
+    <t>#=VF(B17;A17;-C17) / definindo o valor futuro positivamente</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="8" formatCode="&quot;R$&quot;\ #,##0.00;[Red]\-&quot;R$&quot;\ #,##0.00"/>
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
@@ -112,7 +144,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -122,6 +154,42 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0070C0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -155,7 +223,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -165,9 +233,6 @@
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -179,15 +244,31 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="44" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="8" fontId="4" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="8" fontId="4" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="1" fontId="4" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="4" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="8" fontId="0" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -213,9 +294,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -253,9 +334,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -290,7 +371,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -325,7 +406,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -497,172 +578,278 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="1">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{41EBDCA9-2485-4CAD-ACA3-7C1C9DBC7C74}">
+  <we:reference id="wa200005502" version="1.0.0.13" store="pt-BR" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200005502" version="1.0.0.13" store="WA200005502" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="docId" value="&quot;ijv-4IjBj6oWkTBRuEetv&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+  <we:extLst>
+    <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{7C84B067-C214-45C3-A712-C9D94CD141B2}">
+      <we:customFunctionIdList>
+        <we:customFunctionIds>_xldudf_GPT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_CREATE_PROMPT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_LIST</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_HLIST</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_CLASSIFY</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_TRANSLATE</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_EXTRACT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_TAG</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_CONVERT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_FORMAT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_SUMMARIZE</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_TABLE</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_FILL</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_SPLIT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_HSPLIT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_EDIT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_MATCH</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_VISION</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_WEB</we:customFunctionIds>
+      </we:customFunctionIdList>
+    </a:ext>
+  </we:extLst>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.140625" customWidth="1"/>
-    <col min="3" max="3" width="12.42578125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="13.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="62.140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9.5703125" style="6" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="10.5703125" style="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="8"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
+      <c r="A2" s="7"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="18"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
-    </row>
-    <row r="4" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="10" t="s">
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="G3" s="17" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="10" t="s">
         <v>3</v>
       </c>
       <c r="E4" s="2"/>
+      <c r="G4" s="20" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="12"/>
-      <c r="B5" s="13"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="15"/>
+      <c r="A5" s="11">
+        <v>60</v>
+      </c>
+      <c r="B5" s="12">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="C5" s="13">
+        <v>500</v>
+      </c>
+      <c r="D5" s="21">
+        <f>-FV(B5,A5,C5,0)</f>
+        <v>48107.325856324074</v>
+      </c>
       <c r="E5" s="3"/>
       <c r="F5" s="4"/>
+      <c r="G5" s="22" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="16"/>
+      <c r="A6" s="7"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="14"/>
       <c r="E6" s="3"/>
+      <c r="G6" s="24" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="18"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
-    </row>
-    <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
+      <c r="B7" s="16"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="16"/>
+      <c r="G7" s="25" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="D8" s="10" t="s">
         <v>9</v>
       </c>
       <c r="E8" s="2"/>
+      <c r="G8" s="29" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="12"/>
-      <c r="B9" s="13"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="15"/>
+      <c r="A9" s="11">
+        <v>24</v>
+      </c>
+      <c r="B9" s="12">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="C9" s="13">
+        <v>78</v>
+      </c>
+      <c r="D9" s="23">
+        <f>PV(B9,A9,-C9)</f>
+        <v>1252.5526730352515</v>
+      </c>
       <c r="E9" s="3"/>
       <c r="G9" s="5"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
     </row>
     <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="D12" s="10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="12"/>
-      <c r="B13" s="13"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="14"/>
+      <c r="A13" s="11">
+        <v>24</v>
+      </c>
+      <c r="B13" s="12">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="C13" s="27">
+        <f>PMT(B13,A13,D13)</f>
+        <v>-1551.2213588464913</v>
+      </c>
+      <c r="D13" s="28">
+        <v>35000</v>
+      </c>
       <c r="E13" s="3"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="18" t="s">
+      <c r="A15" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="18"/>
+      <c r="B15" s="16"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
     </row>
     <row r="16" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B16" s="10" t="s">
+      <c r="B16" s="9" t="s">
         <v>1</v>
       </c>
       <c r="C16" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="D16" s="10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="17"/>
-      <c r="B17" s="13"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="26">
+        <f>-NPER(B17,C17,D17)</f>
+        <v>18.24727477297845</v>
+      </c>
+      <c r="B17" s="12">
+        <v>2.4E-2</v>
+      </c>
+      <c r="C17" s="13">
+        <v>1551.22</v>
+      </c>
+      <c r="D17" s="13">
+        <v>35000</v>
+      </c>
+      <c r="E17" s="30">
+        <f>FV(B17,A17,-C17)</f>
+        <v>35000.000000000015</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -678,7 +865,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -687,7 +874,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -810,6 +997,12 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -818,20 +1011,35 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4381392-92DC-4B89-8AFA-6588CC1A289C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4381392-92DC-4B89-8AFA-6588CC1A289C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B629338B-86A2-485E-AA11-BE645D1F817C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E79D577D-E54F-43DB-8E50-C26E4C5F764D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E79D577D-E54F-43DB-8E50-C26E4C5F764D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B629338B-86A2-485E-AA11-BE645D1F817C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>